--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260824.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.10%</t>
+          <t>10.93%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>10.39%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>7.88%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.49%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.62%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1056,51 +1056,51 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>91,463</t>
+          <t>31,310</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>31,310</t>
+          <t>91,463</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1122,90 +1122,90 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,937</t>
+          <t>45,227</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>45,227</t>
+          <t>21,458</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>21,458</t>
+          <t>26,469</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>26,469</t>
+          <t>10,937</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,73 +1232,73 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>72,174</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>72,174</t>
+          <t>140,345</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>140,345</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1342,51 +1342,51 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4,721</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1562,51 +1562,51 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,678</t>
+          <t>3,551</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,551</t>
+          <t>5,678</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>132,266,651</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
